--- a/InputData/elec/RPSDbS/RPS Data by Subregion.xlsx
+++ b/InputData/elec/RPSDbS/RPS Data by Subregion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MaryFrancisSwint\Vensim\eps-southkorea\InputData\elec\RPSDbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCEAE39-C05D-471B-8681-F63E1188C47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71B43C6-203D-418C-A561-48CFA8C0DFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="787" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-3765" windowWidth="38640" windowHeight="21120" tabRatio="787" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1465,12 +1465,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="0.000000"/>
-    <numFmt numFmtId="167" formatCode="#,##0.000"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="43">
     <font>
@@ -2577,7 +2576,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="54">
       <alignment vertical="center"/>
     </xf>
@@ -2684,12 +2683,12 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="51" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="1" xfId="54" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="1" xfId="54" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="39" borderId="16" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="39" borderId="16" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="35" fillId="0" borderId="1" xfId="54" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="35" fillId="0" borderId="1" xfId="54" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="41" borderId="0" xfId="54" applyFont="1" applyFill="1">
@@ -2700,8 +2699,8 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="27" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="54" applyBorder="1" applyAlignment="1">
@@ -2710,7 +2709,7 @@
     <xf numFmtId="0" fontId="36" fillId="41" borderId="1" xfId="54" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="36" fillId="41" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="36" fillId="41" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="44" borderId="0" xfId="54" quotePrefix="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -2720,10 +2719,9 @@
     <xf numFmtId="4" fontId="27" fillId="3" borderId="1" xfId="54" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="27" fillId="3" borderId="1" xfId="54" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="27" fillId="3" borderId="1" xfId="54" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2741,8 +2739,8 @@
     <xf numFmtId="0" fontId="27" fillId="45" borderId="0" xfId="54" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="44" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="27" fillId="44" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="167" fontId="0" fillId="44" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="27" fillId="44" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="54" applyFont="1">
@@ -2751,19 +2749,19 @@
     <xf numFmtId="0" fontId="42" fillId="40" borderId="1" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="41" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="41" fillId="44" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="42" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="167" fontId="41" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="41" fillId="44" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="42" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="42" fillId="44" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="167" fontId="42" fillId="44" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="45" borderId="1" xfId="54" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="41" fillId="45" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="42" fillId="45" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="167" fontId="41" fillId="45" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="42" fillId="45" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="40" borderId="1" xfId="54" applyFont="1" applyFill="1" applyBorder="1">
@@ -2772,13 +2770,76 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="54" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="41" fillId="43" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="0" fillId="43" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="41" fillId="43" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="43" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="41" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="51"/>
+    <xf numFmtId="3" fontId="34" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="34" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="43" borderId="36" xfId="54" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2786,12 +2847,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="36" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="36" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2821,66 +2876,10 @@
     <xf numFmtId="0" fontId="29" fillId="36" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="34" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="34" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="35" borderId="1" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="56">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -3485,7 +3484,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="B33" s="92" t="s">
+      <c r="B33" s="91" t="s">
         <v>421</v>
       </c>
     </row>
@@ -6649,13 +6648,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="113" t="s">
         <v>414</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
       <c r="G1" s="63" t="s">
         <v>415</v>
       </c>
@@ -6673,65 +6672,65 @@
       <c r="S1" s="64"/>
       <c r="T1" s="64"/>
     </row>
-    <row r="2" spans="1:20" s="77" customFormat="1">
-      <c r="A2" s="90" t="s">
+    <row r="2" spans="1:20" s="76" customFormat="1">
+      <c r="A2" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="91">
+      <c r="B2" s="90">
         <v>2020</v>
       </c>
-      <c r="C2" s="91">
+      <c r="C2" s="90">
         <v>2021</v>
       </c>
-      <c r="D2" s="91">
+      <c r="D2" s="90">
         <v>2022</v>
       </c>
-      <c r="E2" s="91">
+      <c r="E2" s="90">
         <v>2023</v>
       </c>
-      <c r="F2" s="91">
+      <c r="F2" s="90">
         <v>2024</v>
       </c>
-      <c r="G2" s="91">
+      <c r="G2" s="90">
         <v>2025</v>
       </c>
-      <c r="H2" s="91">
+      <c r="H2" s="90">
         <v>2026</v>
       </c>
-      <c r="I2" s="91">
+      <c r="I2" s="90">
         <v>2027</v>
       </c>
-      <c r="J2" s="91">
+      <c r="J2" s="90">
         <v>2028</v>
       </c>
-      <c r="K2" s="91">
+      <c r="K2" s="90">
         <v>2029</v>
       </c>
-      <c r="L2" s="91">
+      <c r="L2" s="90">
         <v>2030</v>
       </c>
-      <c r="M2" s="91">
+      <c r="M2" s="90">
         <v>2031</v>
       </c>
-      <c r="N2" s="91">
+      <c r="N2" s="90">
         <v>2032</v>
       </c>
-      <c r="O2" s="91">
+      <c r="O2" s="90">
         <v>2033</v>
       </c>
-      <c r="P2" s="91">
+      <c r="P2" s="90">
         <v>2034</v>
       </c>
-      <c r="Q2" s="91">
+      <c r="Q2" s="90">
         <v>2035</v>
       </c>
-      <c r="R2" s="91">
+      <c r="R2" s="90">
         <v>2036</v>
       </c>
-      <c r="S2" s="91">
+      <c r="S2" s="90">
         <v>2037</v>
       </c>
-      <c r="T2" s="91">
+      <c r="T2" s="90">
         <v>2038</v>
       </c>
     </row>
@@ -6751,7 +6750,7 @@
         <f t="shared" si="0"/>
         <v>9.2200000000000006</v>
       </c>
-      <c r="E3" s="75">
+      <c r="E3" s="74">
         <f>SUM(E4:E5)</f>
         <v>9.6</v>
       </c>
@@ -6779,7 +6778,7 @@
         <f t="shared" si="1"/>
         <v>18.8</v>
       </c>
-      <c r="L3" s="75">
+      <c r="L3" s="74">
         <f t="shared" si="1"/>
         <v>21.7</v>
       </c>
@@ -6799,7 +6798,7 @@
         <f t="shared" si="1"/>
         <v>28.2</v>
       </c>
-      <c r="Q3" s="75">
+      <c r="Q3" s="74">
         <f t="shared" si="1"/>
         <v>29.5</v>
       </c>
@@ -6811,88 +6810,88 @@
         <f t="shared" si="1"/>
         <v>32.1</v>
       </c>
-      <c r="T3" s="75">
+      <c r="T3" s="74">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="77" customFormat="1">
-      <c r="A4" s="78" t="s">
+    <row r="4" spans="1:20" s="76" customFormat="1">
+      <c r="A4" s="77" t="s">
         <v>384</v>
       </c>
-      <c r="B4" s="88">
+      <c r="B4" s="87">
         <f>E16</f>
         <v>6.41</v>
       </c>
-      <c r="C4" s="88">
+      <c r="C4" s="87">
         <f t="shared" ref="C4:D4" si="2">F16</f>
         <v>7.15</v>
       </c>
-      <c r="D4" s="88">
+      <c r="D4" s="87">
         <f t="shared" si="2"/>
         <v>8.0500000000000007</v>
       </c>
-      <c r="E4" s="80">
+      <c r="E4" s="79">
         <f>F24</f>
         <v>8.4</v>
       </c>
-      <c r="F4" s="88">
+      <c r="F4" s="87">
         <f>I16</f>
         <v>9</v>
       </c>
-      <c r="G4" s="81">
+      <c r="G4" s="80">
         <f>G41</f>
         <v>9.8000000000000007</v>
       </c>
-      <c r="H4" s="81">
+      <c r="H4" s="80">
         <f>G43</f>
         <v>10.8</v>
       </c>
-      <c r="I4" s="81">
+      <c r="I4" s="80">
         <f>G45</f>
         <v>12</v>
       </c>
-      <c r="J4" s="81">
+      <c r="J4" s="80">
         <f>G47</f>
         <v>13.7</v>
       </c>
-      <c r="K4" s="81">
+      <c r="K4" s="80">
         <f>G49</f>
         <v>16.100000000000001</v>
       </c>
-      <c r="L4" s="82">
+      <c r="L4" s="81">
         <f>G51</f>
         <v>18.8</v>
       </c>
-      <c r="M4" s="81">
+      <c r="M4" s="80">
         <f>G53</f>
         <v>20.9</v>
       </c>
-      <c r="N4" s="81">
+      <c r="N4" s="80">
         <f>G55</f>
         <v>22.4</v>
       </c>
-      <c r="O4" s="81">
+      <c r="O4" s="80">
         <f>G57</f>
         <v>23.6</v>
       </c>
-      <c r="P4" s="81">
+      <c r="P4" s="80">
         <f>G59</f>
         <v>24.8</v>
       </c>
-      <c r="Q4" s="82">
+      <c r="Q4" s="81">
         <f>G61</f>
         <v>26</v>
       </c>
-      <c r="R4" s="81">
+      <c r="R4" s="80">
         <f>G63</f>
         <v>27.5</v>
       </c>
-      <c r="S4" s="81">
+      <c r="S4" s="80">
         <f>G65</f>
         <v>28.4</v>
       </c>
-      <c r="T4" s="82">
+      <c r="T4" s="81">
         <f>G67</f>
         <v>29.2</v>
       </c>
@@ -6901,23 +6900,23 @@
       <c r="A5" s="60" t="s">
         <v>374</v>
       </c>
-      <c r="B5" s="89">
+      <c r="B5" s="88">
         <f>E17</f>
         <v>1.02</v>
       </c>
-      <c r="C5" s="89">
+      <c r="C5" s="88">
         <f t="shared" ref="C5:D5" si="3">F17</f>
         <v>1.1399999999999999</v>
       </c>
-      <c r="D5" s="89">
+      <c r="D5" s="88">
         <f t="shared" si="3"/>
         <v>1.18</v>
       </c>
-      <c r="E5" s="75">
+      <c r="E5" s="74">
         <f>G24</f>
         <v>1.2</v>
       </c>
-      <c r="F5" s="89">
+      <c r="F5" s="88">
         <f>I17</f>
         <v>2</v>
       </c>
@@ -6941,7 +6940,7 @@
         <f>J49</f>
         <v>2.7</v>
       </c>
-      <c r="L5" s="76">
+      <c r="L5" s="75">
         <f>J51</f>
         <v>2.9</v>
       </c>
@@ -6961,7 +6960,7 @@
         <f>J59</f>
         <v>3.4</v>
       </c>
-      <c r="Q5" s="76">
+      <c r="Q5" s="75">
         <f>J61</f>
         <v>3.5</v>
       </c>
@@ -6973,166 +6972,166 @@
         <f>J65</f>
         <v>3.7</v>
       </c>
-      <c r="T5" s="76">
+      <c r="T5" s="75">
         <f>J67</f>
         <v>3.8</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="77" customFormat="1">
-      <c r="A6" s="83" t="s">
+    <row r="6" spans="1:20" s="76" customFormat="1">
+      <c r="A6" s="82" t="s">
         <v>364</v>
       </c>
-      <c r="B6" s="84">
+      <c r="B6" s="83">
         <f>D73</f>
         <v>29.241489091762098</v>
       </c>
-      <c r="C6" s="84">
+      <c r="C6" s="83">
         <f t="shared" ref="C6:D6" si="4">E73</f>
         <v>27.394683508752465</v>
       </c>
-      <c r="D6" s="84">
+      <c r="D6" s="83">
         <f t="shared" si="4"/>
         <v>29.618775235531629</v>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="79">
         <f>C24</f>
         <v>30.7</v>
       </c>
-      <c r="F6" s="84">
+      <c r="F6" s="83">
         <f>H73</f>
         <v>31.691350417477469</v>
       </c>
-      <c r="G6" s="84" cm="1">
+      <c r="G6" s="83" cm="1">
         <f t="array" ref="G6">TREND(CHOOSE({1,2}, $F$6, $L$6), CHOOSE({1,2}, $F$2, $L$2), G2)</f>
         <v>31.709458681231222</v>
       </c>
-      <c r="H6" s="84" cm="1">
+      <c r="H6" s="83" cm="1">
         <f t="array" ref="H6">TREND(CHOOSE({1,2}, $F$6, $L$6), CHOOSE({1,2}, $F$2, $L$2), H2)</f>
         <v>31.727566944984982</v>
       </c>
-      <c r="I6" s="84" cm="1">
+      <c r="I6" s="83" cm="1">
         <f t="array" ref="I6">TREND(CHOOSE({1,2}, $F$6, $L$6), CHOOSE({1,2}, $F$2, $L$2), I2)</f>
         <v>31.745675208738735</v>
       </c>
-      <c r="J6" s="84" cm="1">
+      <c r="J6" s="83" cm="1">
         <f t="array" ref="J6">TREND(CHOOSE({1,2}, $F$6, $L$6), CHOOSE({1,2}, $F$2, $L$2), J2)</f>
         <v>31.763783472492488</v>
       </c>
-      <c r="K6" s="84" cm="1">
+      <c r="K6" s="83" cm="1">
         <f t="array" ref="K6">TREND(CHOOSE({1,2}, $F$6, $L$6), CHOOSE({1,2}, $F$2, $L$2), K2)</f>
         <v>31.781891736246248</v>
       </c>
-      <c r="L6" s="82">
+      <c r="L6" s="81">
         <f>C26</f>
         <v>31.8</v>
       </c>
-      <c r="M6" s="85" cm="1">
+      <c r="M6" s="84" cm="1">
         <f t="array" ref="M6">TREND(CHOOSE({1,2},$L$6,$Q$6), CHOOSE({1,2},$L$2,$Q$2),M2)</f>
         <v>32.259999999999991</v>
       </c>
-      <c r="N6" s="85" cm="1">
+      <c r="N6" s="84" cm="1">
         <f t="array" ref="N6">TREND(CHOOSE({1,2},$L$6,$Q$6), CHOOSE({1,2},$L$2,$Q$2),N2)</f>
         <v>32.720000000000027</v>
       </c>
-      <c r="O6" s="85" cm="1">
+      <c r="O6" s="84" cm="1">
         <f t="array" ref="O6">TREND(CHOOSE({1,2},$L$6,$Q$6), CHOOSE({1,2},$L$2,$Q$2),O2)</f>
         <v>33.180000000000064</v>
       </c>
-      <c r="P6" s="85" cm="1">
+      <c r="P6" s="84" cm="1">
         <f t="array" ref="P6">TREND(CHOOSE({1,2},$L$6,$Q$6), CHOOSE({1,2},$L$2,$Q$2),P2)</f>
         <v>33.639999999999986</v>
       </c>
-      <c r="Q6" s="82">
+      <c r="Q6" s="81">
         <f>C28</f>
         <v>34.1</v>
       </c>
-      <c r="R6" s="85" cm="1">
+      <c r="R6" s="84" cm="1">
         <f t="array" ref="R6">TREND(CHOOSE({1,2},$Q$6,$T$6), CHOOSE({1,2}, $Q$2,$T$2),R2)</f>
         <v>34.466666666666697</v>
       </c>
-      <c r="S6" s="85" cm="1">
+      <c r="S6" s="84" cm="1">
         <f t="array" ref="S6">TREND(CHOOSE({1,2},$Q$6,$T$6), CHOOSE({1,2}, $Q$2,$T$2),S2)</f>
         <v>34.833333333333371</v>
       </c>
-      <c r="T6" s="82">
+      <c r="T6" s="81">
         <f>C30</f>
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="77" customFormat="1">
-      <c r="A7" s="86" t="s">
+    <row r="7" spans="1:20" s="76" customFormat="1">
+      <c r="A7" s="85" t="s">
         <v>419</v>
       </c>
-      <c r="B7" s="79">
-        <v>0</v>
-      </c>
-      <c r="C7" s="79">
-        <v>0</v>
-      </c>
-      <c r="D7" s="79">
-        <v>0</v>
-      </c>
-      <c r="E7" s="80">
+      <c r="B7" s="78">
+        <v>0</v>
+      </c>
+      <c r="C7" s="78">
+        <v>0</v>
+      </c>
+      <c r="D7" s="78">
+        <v>0</v>
+      </c>
+      <c r="E7" s="79">
         <f>H24</f>
         <v>0</v>
       </c>
-      <c r="F7" s="79" cm="1">
+      <c r="F7" s="78" cm="1">
         <f t="array" ref="F7">TREND(CHOOSE({1,2},$E$7,$L$7), CHOOSE({1,2},$E$2,$L$2), F2)</f>
         <v>0.34285714285726954</v>
       </c>
-      <c r="G7" s="79" cm="1">
+      <c r="G7" s="78" cm="1">
         <f t="array" ref="G7">TREND(CHOOSE({1,2},$E$7,$L$7), CHOOSE({1,2},$E$2,$L$2), G2)</f>
         <v>0.68571428571442539</v>
       </c>
-      <c r="H7" s="79" cm="1">
+      <c r="H7" s="78" cm="1">
         <f t="array" ref="H7">TREND(CHOOSE({1,2},$E$7,$L$7), CHOOSE({1,2},$E$2,$L$2), H2)</f>
         <v>1.0285714285715812</v>
       </c>
-      <c r="I7" s="79" cm="1">
+      <c r="I7" s="78" cm="1">
         <f t="array" ref="I7">TREND(CHOOSE({1,2},$E$7,$L$7), CHOOSE({1,2},$E$2,$L$2), I2)</f>
         <v>1.3714285714286234</v>
       </c>
-      <c r="J7" s="79" cm="1">
+      <c r="J7" s="78" cm="1">
         <f t="array" ref="J7">TREND(CHOOSE({1,2},$E$7,$L$7), CHOOSE({1,2},$E$2,$L$2), J2)</f>
         <v>1.7142857142857792</v>
       </c>
-      <c r="K7" s="79" cm="1">
+      <c r="K7" s="78" cm="1">
         <f t="array" ref="K7">TREND(CHOOSE({1,2},$E$7,$L$7), CHOOSE({1,2},$E$2,$L$2), K2)</f>
         <v>2.0571428571429351</v>
       </c>
-      <c r="L7" s="82">
+      <c r="L7" s="81">
         <f>H26</f>
         <v>2.4</v>
       </c>
-      <c r="M7" s="81" cm="1">
+      <c r="M7" s="80" cm="1">
         <f t="array" ref="M7">TREND(CHOOSE({1,2},$L$7,$Q$7), CHOOSE({1,2},$L$2,$Q$2),M2)</f>
         <v>2.8599999999999</v>
       </c>
-      <c r="N7" s="81" cm="1">
+      <c r="N7" s="80" cm="1">
         <f t="array" ref="N7">TREND(CHOOSE({1,2},$L$7,$Q$7), CHOOSE({1,2},$L$2,$Q$2),N2)</f>
         <v>3.3199999999999363</v>
       </c>
-      <c r="O7" s="81" cm="1">
+      <c r="O7" s="80" cm="1">
         <f t="array" ref="O7">TREND(CHOOSE({1,2},$L$7,$Q$7), CHOOSE({1,2},$L$2,$Q$2),O2)</f>
         <v>3.7799999999999727</v>
       </c>
-      <c r="P7" s="81" cm="1">
+      <c r="P7" s="80" cm="1">
         <f t="array" ref="P7">TREND(CHOOSE({1,2},$L$7,$Q$7), CHOOSE({1,2},$L$2,$Q$2),P2)</f>
         <v>4.2399999999998954</v>
       </c>
-      <c r="Q7" s="82">
+      <c r="Q7" s="81">
         <f>H28</f>
         <v>4.7</v>
       </c>
-      <c r="R7" s="81" cm="1">
+      <c r="R7" s="80" cm="1">
         <f t="array" ref="R7">TREND(CHOOSE({1,2},$Q$7,$T$7), CHOOSE({1,2}, $Q$2,$T$2),R2)</f>
         <v>5.2000000000000455</v>
       </c>
-      <c r="S7" s="81" cm="1">
+      <c r="S7" s="80" cm="1">
         <f t="array" ref="S7">TREND(CHOOSE({1,2},$Q$7,$T$7), CHOOSE({1,2}, $Q$2,$T$2),S2)</f>
         <v>5.7000000000000455</v>
       </c>
-      <c r="T7" s="82">
+      <c r="T7" s="81">
         <f>H30</f>
         <v>6.2</v>
       </c>
@@ -7219,7 +7218,7 @@
       </c>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" s="87" t="s">
+      <c r="A9" s="86" t="s">
         <v>420</v>
       </c>
       <c r="B9" s="31"/>
@@ -7257,8 +7256,8 @@
       <c r="E12" s="31"/>
       <c r="F12" s="31"/>
     </row>
-    <row r="13" spans="1:20" s="72" customFormat="1">
-      <c r="A13" s="71" t="s">
+    <row r="13" spans="1:20" s="71" customFormat="1">
+      <c r="A13" s="70" t="s">
         <v>412</v>
       </c>
     </row>
@@ -7377,11 +7376,11 @@
       <c r="A19" s="64" t="s">
         <v>416</v>
       </c>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="10" t="s">
@@ -7394,61 +7393,61 @@
       <c r="F20" s="31"/>
     </row>
     <row r="21" spans="1:13" ht="17.149999999999999" customHeight="1">
-      <c r="A21" s="94" t="s">
+      <c r="A21" s="114" t="s">
         <v>372</v>
       </c>
-      <c r="B21" s="98" t="s">
+      <c r="B21" s="116" t="s">
         <v>373</v>
       </c>
-      <c r="C21" s="98" t="s">
+      <c r="C21" s="116" t="s">
         <v>364</v>
       </c>
-      <c r="D21" s="98" t="s">
+      <c r="D21" s="116" t="s">
         <v>365</v>
       </c>
-      <c r="E21" s="98" t="s">
+      <c r="E21" s="116" t="s">
         <v>167</v>
       </c>
-      <c r="F21" s="100" t="s">
+      <c r="F21" s="118" t="s">
         <v>366</v>
       </c>
-      <c r="G21" s="100" t="s">
+      <c r="G21" s="118" t="s">
         <v>374</v>
       </c>
-      <c r="H21" s="98" t="s">
+      <c r="H21" s="116" t="s">
         <v>375</v>
       </c>
-      <c r="I21" s="98" t="s">
+      <c r="I21" s="116" t="s">
         <v>369</v>
       </c>
-      <c r="J21" s="102" t="s">
+      <c r="J21" s="120" t="s">
         <v>363</v>
       </c>
       <c r="K21" s="14"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="104"/>
+      <c r="L21" s="122"/>
+      <c r="M21" s="122"/>
     </row>
     <row r="22" spans="1:13" ht="35">
-      <c r="A22" s="95"/>
-      <c r="B22" s="99"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="101"/>
-      <c r="H22" s="99"/>
-      <c r="I22" s="99"/>
-      <c r="J22" s="103"/>
-      <c r="K22" s="105" t="s">
+      <c r="A22" s="115"/>
+      <c r="B22" s="117"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="123" t="s">
         <v>376</v>
       </c>
-      <c r="L22" s="106"/>
+      <c r="L22" s="124"/>
       <c r="M22" s="15" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="17.649999999999999" customHeight="1">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="67" t="s">
         <v>402</v>
       </c>
       <c r="B23" s="17" t="s">
@@ -7463,10 +7462,10 @@
       <c r="E23" s="18">
         <v>157.69999999999999</v>
       </c>
-      <c r="F23" s="69">
+      <c r="F23" s="68">
         <v>49.4</v>
       </c>
-      <c r="G23" s="69">
+      <c r="G23" s="68">
         <v>7.2</v>
       </c>
       <c r="H23" s="18" t="s">
@@ -7478,10 +7477,10 @@
       <c r="J23" s="18">
         <v>588</v>
       </c>
-      <c r="K23" s="96">
+      <c r="K23" s="109">
         <v>358.2</v>
       </c>
-      <c r="L23" s="97"/>
+      <c r="L23" s="110"/>
       <c r="M23" s="19">
         <v>229.9</v>
       </c>
@@ -7502,10 +7501,10 @@
       <c r="E24" s="21">
         <v>26.8</v>
       </c>
-      <c r="F24" s="70">
+      <c r="F24" s="69">
         <v>8.4</v>
       </c>
-      <c r="G24" s="70">
+      <c r="G24" s="69">
         <v>1.2</v>
       </c>
       <c r="H24" s="21">
@@ -7517,10 +7516,10 @@
       <c r="J24" s="21">
         <v>100</v>
       </c>
-      <c r="K24" s="109">
+      <c r="K24" s="111">
         <v>60.9</v>
       </c>
-      <c r="L24" s="110"/>
+      <c r="L24" s="112"/>
       <c r="M24" s="22">
         <v>39.1</v>
       </c>
@@ -7541,10 +7540,10 @@
       <c r="E25" s="18">
         <v>161</v>
       </c>
-      <c r="F25" s="69">
+      <c r="F25" s="68">
         <v>120.9</v>
       </c>
-      <c r="G25" s="69">
+      <c r="G25" s="68">
         <v>18.7</v>
       </c>
       <c r="H25" s="18">
@@ -7556,10 +7555,10 @@
       <c r="J25" s="18">
         <v>642.6</v>
       </c>
-      <c r="K25" s="96">
+      <c r="K25" s="109">
         <v>302</v>
       </c>
-      <c r="L25" s="97"/>
+      <c r="L25" s="110"/>
       <c r="M25" s="19">
         <v>340.6</v>
       </c>
@@ -7578,10 +7577,10 @@
       <c r="E26" s="21">
         <v>25.1</v>
       </c>
-      <c r="F26" s="70">
+      <c r="F26" s="69">
         <v>18.8</v>
       </c>
-      <c r="G26" s="70">
+      <c r="G26" s="69">
         <v>2.9</v>
       </c>
       <c r="H26" s="21">
@@ -7593,10 +7592,10 @@
       <c r="J26" s="21">
         <v>100</v>
       </c>
-      <c r="K26" s="109">
+      <c r="K26" s="111">
         <v>47</v>
       </c>
-      <c r="L26" s="110"/>
+      <c r="L26" s="112"/>
       <c r="M26" s="22">
         <v>53</v>
       </c>
@@ -7617,10 +7616,10 @@
       <c r="E27" s="18">
         <v>101.1</v>
       </c>
-      <c r="F27" s="69">
+      <c r="F27" s="68">
         <v>179.9</v>
       </c>
-      <c r="G27" s="69">
+      <c r="G27" s="68">
         <v>24.3</v>
       </c>
       <c r="H27" s="18">
@@ -7632,10 +7631,10 @@
       <c r="J27" s="18">
         <v>691.5</v>
       </c>
-      <c r="K27" s="96">
+      <c r="K27" s="109">
         <v>242.8</v>
       </c>
-      <c r="L27" s="97"/>
+      <c r="L27" s="110"/>
       <c r="M27" s="19">
         <v>448.7</v>
       </c>
@@ -7654,10 +7653,10 @@
       <c r="E28" s="21">
         <v>14.6</v>
       </c>
-      <c r="F28" s="70">
+      <c r="F28" s="69">
         <v>26</v>
       </c>
-      <c r="G28" s="70">
+      <c r="G28" s="69">
         <v>3.5</v>
       </c>
       <c r="H28" s="21">
@@ -7669,10 +7668,10 @@
       <c r="J28" s="21">
         <v>100</v>
       </c>
-      <c r="K28" s="109">
+      <c r="K28" s="111">
         <v>35.1</v>
       </c>
-      <c r="L28" s="110"/>
+      <c r="L28" s="112"/>
       <c r="M28" s="22">
         <v>64.900000000000006</v>
       </c>
@@ -7693,10 +7692,10 @@
       <c r="E29" s="18">
         <v>74.3</v>
       </c>
-      <c r="F29" s="69">
+      <c r="F29" s="68">
         <v>205.7</v>
       </c>
-      <c r="G29" s="69">
+      <c r="G29" s="68">
         <v>26.4</v>
       </c>
       <c r="H29" s="18">
@@ -7708,10 +7707,10 @@
       <c r="J29" s="18">
         <v>704.5</v>
       </c>
-      <c r="K29" s="96">
+      <c r="K29" s="109">
         <v>206.7</v>
       </c>
-      <c r="L29" s="97"/>
+      <c r="L29" s="110"/>
       <c r="M29" s="19">
         <v>497.8</v>
       </c>
@@ -7730,10 +7729,10 @@
       <c r="E30" s="21">
         <v>10.6</v>
       </c>
-      <c r="F30" s="70">
+      <c r="F30" s="69">
         <v>29.2</v>
       </c>
-      <c r="G30" s="70">
+      <c r="G30" s="69">
         <v>3.8</v>
       </c>
       <c r="H30" s="21">
@@ -7745,10 +7744,10 @@
       <c r="J30" s="21">
         <v>100</v>
       </c>
-      <c r="K30" s="109">
+      <c r="K30" s="111">
         <v>29.3</v>
       </c>
-      <c r="L30" s="110"/>
+      <c r="L30" s="112"/>
       <c r="M30" s="22">
         <v>70.7</v>
       </c>
@@ -7764,22 +7763,22 @@
       </c>
     </row>
     <row r="34" spans="1:20">
-      <c r="A34" s="111" t="s">
+      <c r="A34" s="98" t="s">
         <v>372</v>
       </c>
-      <c r="B34" s="114" t="s">
+      <c r="B34" s="101" t="s">
         <v>382</v>
       </c>
-      <c r="C34" s="115"/>
-      <c r="D34" s="115"/>
-      <c r="E34" s="115"/>
-      <c r="F34" s="115"/>
-      <c r="G34" s="115"/>
-      <c r="H34" s="115"/>
-      <c r="I34" s="115"/>
-      <c r="J34" s="115"/>
-      <c r="K34" s="116"/>
-      <c r="L34" s="117" t="s">
+      <c r="C34" s="102"/>
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="102"/>
+      <c r="I34" s="102"/>
+      <c r="J34" s="102"/>
+      <c r="K34" s="103"/>
+      <c r="L34" s="104" t="s">
         <v>383</v>
       </c>
       <c r="M34" s="33" t="s">
@@ -7787,43 +7786,43 @@
       </c>
     </row>
     <row r="35" spans="1:20">
-      <c r="A35" s="112"/>
-      <c r="B35" s="114" t="s">
+      <c r="A35" s="99"/>
+      <c r="B35" s="101" t="s">
         <v>384</v>
       </c>
-      <c r="C35" s="115"/>
-      <c r="D35" s="115"/>
-      <c r="E35" s="115"/>
-      <c r="F35" s="115"/>
-      <c r="G35" s="116"/>
-      <c r="H35" s="114" t="s">
+      <c r="C35" s="102"/>
+      <c r="D35" s="102"/>
+      <c r="E35" s="102"/>
+      <c r="F35" s="102"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="101" t="s">
         <v>374</v>
       </c>
-      <c r="I35" s="115"/>
-      <c r="J35" s="116"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="103"/>
       <c r="K35" s="32" t="s">
         <v>363</v>
       </c>
-      <c r="L35" s="118"/>
+      <c r="L35" s="105"/>
       <c r="M35" s="34" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="36" spans="1:20">
-      <c r="A36" s="112"/>
-      <c r="B36" s="117" t="s">
+      <c r="A36" s="99"/>
+      <c r="B36" s="104" t="s">
         <v>386</v>
       </c>
-      <c r="C36" s="117" t="s">
+      <c r="C36" s="104" t="s">
         <v>387</v>
       </c>
-      <c r="D36" s="117" t="s">
+      <c r="D36" s="104" t="s">
         <v>388</v>
       </c>
-      <c r="E36" s="117" t="s">
+      <c r="E36" s="104" t="s">
         <v>389</v>
       </c>
-      <c r="F36" s="117" t="s">
+      <c r="F36" s="104" t="s">
         <v>390</v>
       </c>
       <c r="G36" s="32" t="s">
@@ -7832,7 +7831,7 @@
       <c r="H36" s="32" t="s">
         <v>392</v>
       </c>
-      <c r="I36" s="117" t="s">
+      <c r="I36" s="104" t="s">
         <v>355</v>
       </c>
       <c r="J36" s="32" t="s">
@@ -7841,56 +7840,56 @@
       <c r="K36" s="37" t="s">
         <v>385</v>
       </c>
-      <c r="L36" s="118"/>
+      <c r="L36" s="105"/>
       <c r="M36" s="35"/>
     </row>
     <row r="37" spans="1:20">
-      <c r="A37" s="113"/>
-      <c r="B37" s="119"/>
-      <c r="C37" s="119"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="119"/>
+      <c r="A37" s="100"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
       <c r="G37" s="39" t="s">
         <v>385</v>
       </c>
       <c r="H37" s="40" t="s">
         <v>392</v>
       </c>
-      <c r="I37" s="119"/>
+      <c r="I37" s="106"/>
       <c r="J37" s="39" t="s">
         <v>385</v>
       </c>
       <c r="K37" s="38"/>
-      <c r="L37" s="119"/>
+      <c r="L37" s="106"/>
       <c r="M37" s="36"/>
     </row>
     <row r="38" spans="1:20">
-      <c r="A38" s="122">
+      <c r="A38" s="96">
         <v>2024</v>
       </c>
-      <c r="B38" s="120">
+      <c r="B38" s="92">
         <v>34160</v>
       </c>
-      <c r="C38" s="120">
+      <c r="C38" s="92">
         <v>4330</v>
       </c>
-      <c r="D38" s="120">
+      <c r="D38" s="92">
         <v>3633</v>
       </c>
-      <c r="E38" s="124">
+      <c r="E38" s="94">
         <v>446</v>
       </c>
-      <c r="F38" s="120">
+      <c r="F38" s="92">
         <v>11146</v>
       </c>
       <c r="G38" s="42">
         <v>53716</v>
       </c>
-      <c r="H38" s="120">
+      <c r="H38" s="92">
         <v>7277</v>
       </c>
-      <c r="I38" s="120">
+      <c r="I38" s="92">
         <v>2182</v>
       </c>
       <c r="J38" s="42">
@@ -7899,7 +7898,7 @@
       <c r="K38" s="42">
         <v>63174</v>
       </c>
-      <c r="L38" s="120">
+      <c r="L38" s="92">
         <v>5956</v>
       </c>
       <c r="M38" s="44">
@@ -7908,55 +7907,55 @@
       <c r="N38" s="48"/>
     </row>
     <row r="39" spans="1:20">
-      <c r="A39" s="123"/>
-      <c r="B39" s="121"/>
-      <c r="C39" s="121"/>
-      <c r="D39" s="121"/>
-      <c r="E39" s="125"/>
-      <c r="F39" s="121"/>
+      <c r="A39" s="97"/>
+      <c r="B39" s="93"/>
+      <c r="C39" s="93"/>
+      <c r="D39" s="93"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="93"/>
       <c r="G39" s="43">
         <v>9</v>
       </c>
-      <c r="H39" s="121"/>
-      <c r="I39" s="121"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="93"/>
       <c r="J39" s="43">
         <v>1.6</v>
       </c>
       <c r="K39" s="43">
         <v>10.5</v>
       </c>
-      <c r="L39" s="121"/>
+      <c r="L39" s="93"/>
       <c r="M39" s="45">
         <v>10.8</v>
       </c>
       <c r="N39" s="48"/>
     </row>
     <row r="40" spans="1:20">
-      <c r="A40" s="122">
+      <c r="A40" s="96">
         <v>2025</v>
       </c>
-      <c r="B40" s="120">
+      <c r="B40" s="92">
         <v>39140</v>
       </c>
-      <c r="C40" s="120">
+      <c r="C40" s="92">
         <v>5255</v>
       </c>
-      <c r="D40" s="120">
+      <c r="D40" s="92">
         <v>3712</v>
       </c>
-      <c r="E40" s="124">
+      <c r="E40" s="94">
         <v>445</v>
       </c>
-      <c r="F40" s="120">
+      <c r="F40" s="92">
         <v>11164</v>
       </c>
       <c r="G40" s="42">
         <v>59716</v>
       </c>
-      <c r="H40" s="120">
+      <c r="H40" s="92">
         <v>8832</v>
       </c>
-      <c r="I40" s="120">
+      <c r="I40" s="92">
         <v>2176</v>
       </c>
       <c r="J40" s="42">
@@ -7965,7 +7964,7 @@
       <c r="K40" s="42">
         <v>70723</v>
       </c>
-      <c r="L40" s="120">
+      <c r="L40" s="92">
         <v>6549</v>
       </c>
       <c r="M40" s="44">
@@ -7980,24 +7979,24 @@
       <c r="T40" s="48"/>
     </row>
     <row r="41" spans="1:20">
-      <c r="A41" s="123"/>
-      <c r="B41" s="121"/>
-      <c r="C41" s="121"/>
-      <c r="D41" s="121"/>
-      <c r="E41" s="125"/>
-      <c r="F41" s="121"/>
+      <c r="A41" s="97"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="95"/>
+      <c r="F41" s="93"/>
       <c r="G41" s="43">
         <v>9.8000000000000007</v>
       </c>
-      <c r="H41" s="121"/>
-      <c r="I41" s="121"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
       <c r="J41" s="43">
         <v>1.8</v>
       </c>
       <c r="K41" s="43">
         <v>11.7</v>
       </c>
-      <c r="L41" s="121"/>
+      <c r="L41" s="93"/>
       <c r="M41" s="45">
         <v>11.9</v>
       </c>
@@ -8010,31 +8009,31 @@
       <c r="T41" s="48"/>
     </row>
     <row r="42" spans="1:20">
-      <c r="A42" s="122">
+      <c r="A42" s="96">
         <v>2026</v>
       </c>
-      <c r="B42" s="120">
+      <c r="B42" s="92">
         <v>44154</v>
       </c>
-      <c r="C42" s="120">
+      <c r="C42" s="92">
         <v>6889</v>
       </c>
-      <c r="D42" s="120">
+      <c r="D42" s="92">
         <v>3712</v>
       </c>
-      <c r="E42" s="124">
+      <c r="E42" s="94">
         <v>445</v>
       </c>
-      <c r="F42" s="120">
+      <c r="F42" s="92">
         <v>10870</v>
       </c>
       <c r="G42" s="42">
         <v>66070</v>
       </c>
-      <c r="H42" s="120">
+      <c r="H42" s="92">
         <v>10631</v>
       </c>
-      <c r="I42" s="120">
+      <c r="I42" s="92">
         <v>2176</v>
       </c>
       <c r="J42" s="42">
@@ -8043,7 +8042,7 @@
       <c r="K42" s="42">
         <v>78877</v>
       </c>
-      <c r="L42" s="120">
+      <c r="L42" s="92">
         <v>7212</v>
       </c>
       <c r="M42" s="44">
@@ -8058,24 +8057,24 @@
       <c r="T42" s="48"/>
     </row>
     <row r="43" spans="1:20">
-      <c r="A43" s="123"/>
-      <c r="B43" s="121"/>
-      <c r="C43" s="121"/>
-      <c r="D43" s="121"/>
-      <c r="E43" s="125"/>
-      <c r="F43" s="121"/>
+      <c r="A43" s="97"/>
+      <c r="B43" s="93"/>
+      <c r="C43" s="93"/>
+      <c r="D43" s="93"/>
+      <c r="E43" s="95"/>
+      <c r="F43" s="93"/>
       <c r="G43" s="43">
         <v>10.8</v>
       </c>
-      <c r="H43" s="121"/>
-      <c r="I43" s="121"/>
+      <c r="H43" s="93"/>
+      <c r="I43" s="93"/>
       <c r="J43" s="43">
         <v>2.1</v>
       </c>
       <c r="K43" s="43">
         <v>12.8</v>
       </c>
-      <c r="L43" s="121"/>
+      <c r="L43" s="93"/>
       <c r="M43" s="45">
         <v>13.1</v>
       </c>
@@ -8088,31 +8087,31 @@
       <c r="T43" s="48"/>
     </row>
     <row r="44" spans="1:20">
-      <c r="A44" s="122">
+      <c r="A44" s="96">
         <v>2027</v>
       </c>
-      <c r="B44" s="120">
+      <c r="B44" s="92">
         <v>49055</v>
       </c>
-      <c r="C44" s="120">
+      <c r="C44" s="92">
         <v>10369</v>
       </c>
-      <c r="D44" s="120">
+      <c r="D44" s="92">
         <v>3712</v>
       </c>
-      <c r="E44" s="124">
+      <c r="E44" s="94">
         <v>445</v>
       </c>
-      <c r="F44" s="120">
+      <c r="F44" s="92">
         <v>10863</v>
       </c>
       <c r="G44" s="42">
         <v>74445</v>
       </c>
-      <c r="H44" s="120">
+      <c r="H44" s="92">
         <v>12179</v>
       </c>
-      <c r="I44" s="120">
+      <c r="I44" s="92">
         <v>2176</v>
       </c>
       <c r="J44" s="42">
@@ -8121,7 +8120,7 @@
       <c r="K44" s="42">
         <v>88799</v>
       </c>
-      <c r="L44" s="120">
+      <c r="L44" s="92">
         <v>7896</v>
       </c>
       <c r="M44" s="44">
@@ -8136,24 +8135,24 @@
       <c r="T44" s="48"/>
     </row>
     <row r="45" spans="1:20">
-      <c r="A45" s="123"/>
-      <c r="B45" s="121"/>
-      <c r="C45" s="121"/>
-      <c r="D45" s="121"/>
-      <c r="E45" s="125"/>
-      <c r="F45" s="121"/>
+      <c r="A45" s="97"/>
+      <c r="B45" s="93"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="95"/>
+      <c r="F45" s="93"/>
       <c r="G45" s="43">
         <v>12</v>
       </c>
-      <c r="H45" s="121"/>
-      <c r="I45" s="121"/>
+      <c r="H45" s="93"/>
+      <c r="I45" s="93"/>
       <c r="J45" s="43">
         <v>2.2999999999999998</v>
       </c>
       <c r="K45" s="43">
         <v>14.3</v>
       </c>
-      <c r="L45" s="121"/>
+      <c r="L45" s="93"/>
       <c r="M45" s="45">
         <v>14.5</v>
       </c>
@@ -8178,19 +8177,19 @@
       <c r="D46" s="42">
         <v>3722</v>
       </c>
-      <c r="E46" s="124">
+      <c r="E46" s="94">
         <v>446</v>
       </c>
-      <c r="F46" s="120">
+      <c r="F46" s="92">
         <v>10878</v>
       </c>
       <c r="G46" s="42">
         <v>86001</v>
       </c>
-      <c r="H46" s="120">
+      <c r="H46" s="92">
         <v>13656</v>
       </c>
-      <c r="I46" s="120">
+      <c r="I46" s="92">
         <v>2182</v>
       </c>
       <c r="J46" s="42">
@@ -8199,7 +8198,7 @@
       <c r="K46" s="42">
         <v>101839</v>
       </c>
-      <c r="L46" s="120">
+      <c r="L46" s="92">
         <v>8626</v>
       </c>
       <c r="M46" s="44">
@@ -8218,20 +8217,20 @@
       <c r="B47" s="47"/>
       <c r="C47" s="47"/>
       <c r="D47" s="47"/>
-      <c r="E47" s="125"/>
-      <c r="F47" s="121"/>
+      <c r="E47" s="95"/>
+      <c r="F47" s="93"/>
       <c r="G47" s="43">
         <v>13.7</v>
       </c>
-      <c r="H47" s="121"/>
-      <c r="I47" s="121"/>
+      <c r="H47" s="93"/>
+      <c r="I47" s="93"/>
       <c r="J47" s="43">
         <v>2.5</v>
       </c>
       <c r="K47" s="43">
         <v>16.2</v>
       </c>
-      <c r="L47" s="121"/>
+      <c r="L47" s="93"/>
       <c r="M47" s="45">
         <v>16.3</v>
       </c>
@@ -8256,19 +8255,19 @@
       <c r="D48" s="42">
         <v>3712</v>
       </c>
-      <c r="E48" s="124">
+      <c r="E48" s="94">
         <v>445</v>
       </c>
-      <c r="F48" s="120">
+      <c r="F48" s="92">
         <v>10846</v>
       </c>
       <c r="G48" s="42">
         <v>102096</v>
       </c>
-      <c r="H48" s="120">
+      <c r="H48" s="92">
         <v>15059</v>
       </c>
-      <c r="I48" s="120">
+      <c r="I48" s="92">
         <v>2176</v>
       </c>
       <c r="J48" s="42">
@@ -8277,7 +8276,7 @@
       <c r="K48" s="42">
         <v>119331</v>
       </c>
-      <c r="L48" s="120">
+      <c r="L48" s="92">
         <v>9328</v>
       </c>
       <c r="M48" s="44">
@@ -8296,20 +8295,20 @@
       <c r="B49" s="47"/>
       <c r="C49" s="47"/>
       <c r="D49" s="47"/>
-      <c r="E49" s="125"/>
-      <c r="F49" s="121"/>
+      <c r="E49" s="95"/>
+      <c r="F49" s="93"/>
       <c r="G49" s="43">
         <v>16.100000000000001</v>
       </c>
-      <c r="H49" s="121"/>
-      <c r="I49" s="121"/>
+      <c r="H49" s="93"/>
+      <c r="I49" s="93"/>
       <c r="J49" s="43">
         <v>2.7</v>
       </c>
       <c r="K49" s="43">
         <v>18.8</v>
       </c>
-      <c r="L49" s="121"/>
+      <c r="L49" s="93"/>
       <c r="M49" s="45">
         <v>18.899999999999999</v>
       </c>
@@ -8334,19 +8333,19 @@
       <c r="D50" s="42">
         <v>3712</v>
       </c>
-      <c r="E50" s="124">
+      <c r="E50" s="94">
         <v>445</v>
       </c>
-      <c r="F50" s="120">
+      <c r="F50" s="92">
         <v>10814</v>
       </c>
       <c r="G50" s="42">
         <v>120920</v>
       </c>
-      <c r="H50" s="120">
+      <c r="H50" s="92">
         <v>16500</v>
       </c>
-      <c r="I50" s="120">
+      <c r="I50" s="92">
         <v>2176</v>
       </c>
       <c r="J50" s="42">
@@ -8355,7 +8354,7 @@
       <c r="K50" s="42">
         <v>139595</v>
       </c>
-      <c r="L50" s="120">
+      <c r="L50" s="92">
         <v>10071</v>
       </c>
       <c r="M50" s="44">
@@ -8374,20 +8373,20 @@
       <c r="B51" s="47"/>
       <c r="C51" s="47"/>
       <c r="D51" s="47"/>
-      <c r="E51" s="125"/>
-      <c r="F51" s="121"/>
+      <c r="E51" s="95"/>
+      <c r="F51" s="93"/>
       <c r="G51" s="43">
         <v>18.8</v>
       </c>
-      <c r="H51" s="121"/>
-      <c r="I51" s="121"/>
+      <c r="H51" s="93"/>
+      <c r="I51" s="93"/>
       <c r="J51" s="43">
         <v>2.9</v>
       </c>
       <c r="K51" s="43">
         <v>21.7</v>
       </c>
-      <c r="L51" s="121"/>
+      <c r="L51" s="93"/>
       <c r="M51" s="45">
         <v>21.7</v>
       </c>
@@ -8412,19 +8411,19 @@
       <c r="D52" s="42">
         <v>3712</v>
       </c>
-      <c r="E52" s="124">
+      <c r="E52" s="94">
         <v>445</v>
       </c>
-      <c r="F52" s="120">
+      <c r="F52" s="92">
         <v>10815</v>
       </c>
       <c r="G52" s="42">
         <v>136599</v>
       </c>
-      <c r="H52" s="120">
+      <c r="H52" s="92">
         <v>17760</v>
       </c>
-      <c r="I52" s="120">
+      <c r="I52" s="92">
         <v>2176</v>
       </c>
       <c r="J52" s="42">
@@ -8433,7 +8432,7 @@
       <c r="K52" s="42">
         <v>156535</v>
       </c>
-      <c r="L52" s="120">
+      <c r="L52" s="92">
         <v>10824</v>
       </c>
       <c r="M52" s="44">
@@ -8452,20 +8451,20 @@
       <c r="B53" s="47"/>
       <c r="C53" s="47"/>
       <c r="D53" s="47"/>
-      <c r="E53" s="125"/>
-      <c r="F53" s="121"/>
+      <c r="E53" s="95"/>
+      <c r="F53" s="93"/>
       <c r="G53" s="43">
         <v>20.9</v>
       </c>
-      <c r="H53" s="121"/>
-      <c r="I53" s="121"/>
+      <c r="H53" s="93"/>
+      <c r="I53" s="93"/>
       <c r="J53" s="43">
         <v>3</v>
       </c>
       <c r="K53" s="43">
         <v>23.9</v>
       </c>
-      <c r="L53" s="121"/>
+      <c r="L53" s="93"/>
       <c r="M53" s="45">
         <v>23.8</v>
       </c>
@@ -8490,19 +8489,19 @@
       <c r="D54" s="42">
         <v>3722</v>
       </c>
-      <c r="E54" s="124">
+      <c r="E54" s="94">
         <v>446</v>
       </c>
-      <c r="F54" s="120">
+      <c r="F54" s="92">
         <v>10845</v>
       </c>
       <c r="G54" s="42">
         <v>149056</v>
       </c>
-      <c r="H54" s="120">
+      <c r="H54" s="92">
         <v>18892</v>
       </c>
-      <c r="I54" s="120">
+      <c r="I54" s="92">
         <v>2182</v>
       </c>
       <c r="J54" s="42">
@@ -8511,7 +8510,7 @@
       <c r="K54" s="42">
         <v>170130</v>
       </c>
-      <c r="L54" s="120">
+      <c r="L54" s="92">
         <v>11617</v>
       </c>
       <c r="M54" s="44">
@@ -8530,20 +8529,20 @@
       <c r="B55" s="47"/>
       <c r="C55" s="47"/>
       <c r="D55" s="47"/>
-      <c r="E55" s="125"/>
-      <c r="F55" s="121"/>
+      <c r="E55" s="95"/>
+      <c r="F55" s="93"/>
       <c r="G55" s="43">
         <v>22.4</v>
       </c>
-      <c r="H55" s="121"/>
-      <c r="I55" s="121"/>
+      <c r="H55" s="93"/>
+      <c r="I55" s="93"/>
       <c r="J55" s="43">
         <v>3.2</v>
       </c>
       <c r="K55" s="43">
         <v>25.6</v>
       </c>
-      <c r="L55" s="121"/>
+      <c r="L55" s="93"/>
       <c r="M55" s="45">
         <v>25.4</v>
       </c>
@@ -8568,19 +8567,19 @@
       <c r="D56" s="42">
         <v>3712</v>
       </c>
-      <c r="E56" s="124">
+      <c r="E56" s="94">
         <v>445</v>
       </c>
-      <c r="F56" s="120">
+      <c r="F56" s="92">
         <v>10803</v>
       </c>
       <c r="G56" s="42">
         <v>158886</v>
       </c>
-      <c r="H56" s="120">
+      <c r="H56" s="92">
         <v>19920</v>
       </c>
-      <c r="I56" s="120">
+      <c r="I56" s="92">
         <v>2176</v>
       </c>
       <c r="J56" s="42">
@@ -8589,7 +8588,7 @@
       <c r="K56" s="42">
         <v>180982</v>
       </c>
-      <c r="L56" s="120">
+      <c r="L56" s="92">
         <v>12363</v>
       </c>
       <c r="M56" s="44">
@@ -8608,20 +8607,20 @@
       <c r="B57" s="47"/>
       <c r="C57" s="47"/>
       <c r="D57" s="47"/>
-      <c r="E57" s="125"/>
-      <c r="F57" s="121"/>
+      <c r="E57" s="95"/>
+      <c r="F57" s="93"/>
       <c r="G57" s="43">
         <v>23.6</v>
       </c>
-      <c r="H57" s="121"/>
-      <c r="I57" s="121"/>
+      <c r="H57" s="93"/>
+      <c r="I57" s="93"/>
       <c r="J57" s="43">
         <v>3.3</v>
       </c>
       <c r="K57" s="43">
         <v>26.9</v>
       </c>
-      <c r="L57" s="121"/>
+      <c r="L57" s="93"/>
       <c r="M57" s="45">
         <v>26.7</v>
       </c>
@@ -8646,19 +8645,19 @@
       <c r="D58" s="42">
         <v>3712</v>
       </c>
-      <c r="E58" s="124">
+      <c r="E58" s="94">
         <v>445</v>
       </c>
-      <c r="F58" s="120">
+      <c r="F58" s="92">
         <v>10817</v>
       </c>
       <c r="G58" s="42">
         <v>169108</v>
       </c>
-      <c r="H58" s="120">
+      <c r="H58" s="92">
         <v>21000</v>
       </c>
-      <c r="I58" s="120">
+      <c r="I58" s="92">
         <v>2176</v>
       </c>
       <c r="J58" s="42">
@@ -8667,7 +8666,7 @@
       <c r="K58" s="42">
         <v>192284</v>
       </c>
-      <c r="L58" s="120">
+      <c r="L58" s="92">
         <v>13159</v>
       </c>
       <c r="M58" s="44">
@@ -8686,20 +8685,20 @@
       <c r="B59" s="47"/>
       <c r="C59" s="47"/>
       <c r="D59" s="47"/>
-      <c r="E59" s="125"/>
-      <c r="F59" s="121"/>
+      <c r="E59" s="95"/>
+      <c r="F59" s="93"/>
       <c r="G59" s="43">
         <v>24.8</v>
       </c>
-      <c r="H59" s="121"/>
-      <c r="I59" s="121"/>
+      <c r="H59" s="93"/>
+      <c r="I59" s="93"/>
       <c r="J59" s="43">
         <v>3.4</v>
       </c>
       <c r="K59" s="43">
         <v>28.2</v>
       </c>
-      <c r="L59" s="121"/>
+      <c r="L59" s="93"/>
       <c r="M59" s="45">
         <v>28</v>
       </c>
@@ -8724,19 +8723,19 @@
       <c r="D60" s="42">
         <v>3712</v>
       </c>
-      <c r="E60" s="124">
+      <c r="E60" s="94">
         <v>445</v>
       </c>
-      <c r="F60" s="120">
+      <c r="F60" s="92">
         <v>10799</v>
       </c>
       <c r="G60" s="42">
         <v>179937</v>
       </c>
-      <c r="H60" s="120">
+      <c r="H60" s="92">
         <v>22081</v>
       </c>
-      <c r="I60" s="120">
+      <c r="I60" s="92">
         <v>2176</v>
       </c>
       <c r="J60" s="42">
@@ -8745,7 +8744,7 @@
       <c r="K60" s="42">
         <v>204193</v>
       </c>
-      <c r="L60" s="120">
+      <c r="L60" s="92">
         <v>13973</v>
       </c>
       <c r="M60" s="44">
@@ -8764,20 +8763,20 @@
       <c r="B61" s="47"/>
       <c r="C61" s="47"/>
       <c r="D61" s="47"/>
-      <c r="E61" s="125"/>
-      <c r="F61" s="121"/>
+      <c r="E61" s="95"/>
+      <c r="F61" s="93"/>
       <c r="G61" s="43">
         <v>26</v>
       </c>
-      <c r="H61" s="121"/>
-      <c r="I61" s="121"/>
+      <c r="H61" s="93"/>
+      <c r="I61" s="93"/>
       <c r="J61" s="43">
         <v>3.5</v>
       </c>
       <c r="K61" s="43">
         <v>29.5</v>
       </c>
-      <c r="L61" s="121"/>
+      <c r="L61" s="93"/>
       <c r="M61" s="45">
         <v>29.3</v>
       </c>
@@ -8802,19 +8801,19 @@
       <c r="D62" s="42">
         <v>3722</v>
       </c>
-      <c r="E62" s="124">
+      <c r="E62" s="94">
         <v>446</v>
       </c>
-      <c r="F62" s="120">
+      <c r="F62" s="92">
         <v>10633</v>
       </c>
       <c r="G62" s="42">
         <v>190398</v>
       </c>
-      <c r="H62" s="120">
+      <c r="H62" s="92">
         <v>22745</v>
       </c>
-      <c r="I62" s="120">
+      <c r="I62" s="92">
         <v>2182</v>
       </c>
       <c r="J62" s="42">
@@ -8823,7 +8822,7 @@
       <c r="K62" s="42">
         <v>215325</v>
       </c>
-      <c r="L62" s="120">
+      <c r="L62" s="92">
         <v>14845</v>
       </c>
       <c r="M62" s="44">
@@ -8842,20 +8841,20 @@
       <c r="B63" s="47"/>
       <c r="C63" s="47"/>
       <c r="D63" s="47"/>
-      <c r="E63" s="125"/>
-      <c r="F63" s="121"/>
+      <c r="E63" s="95"/>
+      <c r="F63" s="93"/>
       <c r="G63" s="43">
         <v>27.5</v>
       </c>
-      <c r="H63" s="121"/>
-      <c r="I63" s="121"/>
+      <c r="H63" s="93"/>
+      <c r="I63" s="93"/>
       <c r="J63" s="43">
         <v>3.6</v>
       </c>
       <c r="K63" s="43">
         <v>31.1</v>
       </c>
-      <c r="L63" s="121"/>
+      <c r="L63" s="93"/>
       <c r="M63" s="45">
         <v>30.8</v>
       </c>
@@ -8880,19 +8879,19 @@
       <c r="D64" s="42">
         <v>3712</v>
       </c>
-      <c r="E64" s="124">
+      <c r="E64" s="94">
         <v>445</v>
       </c>
-      <c r="F64" s="120">
+      <c r="F64" s="92">
         <v>10600</v>
       </c>
       <c r="G64" s="42">
         <v>198295</v>
       </c>
-      <c r="H64" s="120">
+      <c r="H64" s="92">
         <v>23565</v>
       </c>
-      <c r="I64" s="120">
+      <c r="I64" s="92">
         <v>2176</v>
       </c>
       <c r="J64" s="42">
@@ -8901,7 +8900,7 @@
       <c r="K64" s="42">
         <v>224035</v>
       </c>
-      <c r="L64" s="120">
+      <c r="L64" s="92">
         <v>15655</v>
       </c>
       <c r="M64" s="44">
@@ -8920,20 +8919,20 @@
       <c r="B65" s="47"/>
       <c r="C65" s="47"/>
       <c r="D65" s="47"/>
-      <c r="E65" s="125"/>
-      <c r="F65" s="121"/>
+      <c r="E65" s="95"/>
+      <c r="F65" s="93"/>
       <c r="G65" s="43">
         <v>28.4</v>
       </c>
-      <c r="H65" s="121"/>
-      <c r="I65" s="121"/>
+      <c r="H65" s="93"/>
+      <c r="I65" s="93"/>
       <c r="J65" s="43">
         <v>3.7</v>
       </c>
       <c r="K65" s="43">
         <v>32.1</v>
       </c>
-      <c r="L65" s="121"/>
+      <c r="L65" s="93"/>
       <c r="M65" s="45">
         <v>31.9</v>
       </c>
@@ -8958,19 +8957,19 @@
       <c r="D66" s="42">
         <v>3712</v>
       </c>
-      <c r="E66" s="124">
+      <c r="E66" s="94">
         <v>445</v>
       </c>
-      <c r="F66" s="120">
+      <c r="F66" s="92">
         <v>10602</v>
       </c>
       <c r="G66" s="42">
         <v>205673</v>
       </c>
-      <c r="H66" s="120">
+      <c r="H66" s="92">
         <v>24270</v>
       </c>
-      <c r="I66" s="120">
+      <c r="I66" s="92">
         <v>2176</v>
       </c>
       <c r="J66" s="42">
@@ -8979,7 +8978,7 @@
       <c r="K66" s="42">
         <v>232119</v>
       </c>
-      <c r="L66" s="120">
+      <c r="L66" s="92">
         <v>16523</v>
       </c>
       <c r="M66" s="44">
@@ -8998,20 +8997,20 @@
       <c r="B67" s="47"/>
       <c r="C67" s="47"/>
       <c r="D67" s="47"/>
-      <c r="E67" s="125"/>
-      <c r="F67" s="121"/>
+      <c r="E67" s="95"/>
+      <c r="F67" s="93"/>
       <c r="G67" s="43">
         <v>29.2</v>
       </c>
-      <c r="H67" s="121"/>
-      <c r="I67" s="121"/>
+      <c r="H67" s="93"/>
+      <c r="I67" s="93"/>
       <c r="J67" s="43">
         <v>3.8</v>
       </c>
       <c r="K67" s="43">
         <v>32.9</v>
       </c>
-      <c r="L67" s="121"/>
+      <c r="L67" s="93"/>
       <c r="M67" s="45">
         <v>32.700000000000003</v>
       </c>
@@ -9023,8 +9022,8 @@
       <c r="S67" s="48"/>
       <c r="T67" s="48"/>
     </row>
-    <row r="69" spans="1:20" s="74" customFormat="1">
-      <c r="A69" s="74" t="s">
+    <row r="69" spans="1:20" s="73" customFormat="1">
+      <c r="A69" s="73" t="s">
         <v>393</v>
       </c>
     </row>
@@ -9321,61 +9320,59 @@
     </row>
   </sheetData>
   <mergeCells count="126">
-    <mergeCell ref="F66:F67"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="I66:I67"/>
-    <mergeCell ref="L66:L67"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="I62:I63"/>
-    <mergeCell ref="L62:L63"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="F64:F65"/>
-    <mergeCell ref="H64:H65"/>
-    <mergeCell ref="I64:I65"/>
-    <mergeCell ref="L64:L65"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="L58:L59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="I60:I61"/>
-    <mergeCell ref="L60:L61"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="L54:L55"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="I56:I57"/>
-    <mergeCell ref="L56:L57"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="L50:L51"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="L52:L53"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="L46:L47"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="L48:L49"/>
-    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:K34"/>
+    <mergeCell ref="L34:L37"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
     <mergeCell ref="F42:F43"/>
     <mergeCell ref="H42:H43"/>
     <mergeCell ref="I42:I43"/>
@@ -9394,59 +9391,61 @@
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="D42:D43"/>
     <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:K34"/>
-    <mergeCell ref="L34:L37"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="L46:L47"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="L48:L49"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="L50:L51"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="L52:L53"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="L54:L55"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="L56:L57"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="L60:L61"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="L66:L67"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="I64:I65"/>
+    <mergeCell ref="L64:L65"/>
+    <mergeCell ref="E62:E63"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11243,10 +11242,10 @@
       </c>
     </row>
     <row r="6" spans="1:87">
-      <c r="A6" s="126" t="s">
+      <c r="A6" s="125" t="s">
         <v>164</v>
       </c>
-      <c r="B6" s="126"/>
+      <c r="B6" s="125"/>
       <c r="C6" s="11" t="s">
         <v>363</v>
       </c>
@@ -11273,7 +11272,7 @@
       </c>
     </row>
     <row r="7" spans="1:87">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="125" t="s">
         <v>170</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -11305,7 +11304,7 @@
       </c>
     </row>
     <row r="8" spans="1:87">
-      <c r="A8" s="126"/>
+      <c r="A8" s="125"/>
       <c r="B8" s="11" t="s">
         <v>371</v>
       </c>
@@ -11335,7 +11334,7 @@
       </c>
     </row>
     <row r="9" spans="1:87">
-      <c r="A9" s="126" t="s">
+      <c r="A9" s="125" t="s">
         <v>187</v>
       </c>
       <c r="B9" s="11" t="s">
@@ -11367,7 +11366,7 @@
       </c>
     </row>
     <row r="10" spans="1:87">
-      <c r="A10" s="126"/>
+      <c r="A10" s="125"/>
       <c r="B10" s="11" t="s">
         <v>371</v>
       </c>
@@ -11397,7 +11396,7 @@
       </c>
     </row>
     <row r="11" spans="1:87">
-      <c r="A11" s="126" t="s">
+      <c r="A11" s="125" t="s">
         <v>201</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -11429,7 +11428,7 @@
       </c>
     </row>
     <row r="12" spans="1:87">
-      <c r="A12" s="126"/>
+      <c r="A12" s="125"/>
       <c r="B12" s="11" t="s">
         <v>371</v>
       </c>
@@ -11459,7 +11458,7 @@
       </c>
     </row>
     <row r="13" spans="1:87">
-      <c r="A13" s="126" t="s">
+      <c r="A13" s="125" t="s">
         <v>215</v>
       </c>
       <c r="B13" s="11" t="s">
@@ -11491,7 +11490,7 @@
       </c>
     </row>
     <row r="14" spans="1:87">
-      <c r="A14" s="126"/>
+      <c r="A14" s="125"/>
       <c r="B14" s="11" t="s">
         <v>371</v>
       </c>
@@ -11521,7 +11520,7 @@
       </c>
     </row>
     <row r="15" spans="1:87">
-      <c r="A15" s="126" t="s">
+      <c r="A15" s="125" t="s">
         <v>228</v>
       </c>
       <c r="B15" s="11" t="s">
@@ -11553,7 +11552,7 @@
       </c>
     </row>
     <row r="16" spans="1:87">
-      <c r="A16" s="126"/>
+      <c r="A16" s="125"/>
       <c r="B16" s="11" t="s">
         <v>371</v>
       </c>
@@ -11583,7 +11582,7 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="126" t="s">
+      <c r="A17" s="125" t="s">
         <v>243</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -11615,7 +11614,7 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="126"/>
+      <c r="A18" s="125"/>
       <c r="B18" s="11" t="s">
         <v>371</v>
       </c>
@@ -11645,7 +11644,7 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="126" t="s">
+      <c r="A19" s="125" t="s">
         <v>257</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -11677,7 +11676,7 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="126"/>
+      <c r="A20" s="125"/>
       <c r="B20" s="11" t="s">
         <v>371</v>
       </c>
@@ -11707,7 +11706,7 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="126" t="s">
+      <c r="A21" s="125" t="s">
         <v>270</v>
       </c>
       <c r="B21" s="11" t="s">
@@ -11739,7 +11738,7 @@
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="126"/>
+      <c r="A22" s="125"/>
       <c r="B22" s="11" t="s">
         <v>371</v>
       </c>
@@ -11769,7 +11768,7 @@
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="126" t="s">
+      <c r="A23" s="125" t="s">
         <v>285</v>
       </c>
       <c r="B23" s="11" t="s">
@@ -11801,7 +11800,7 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="126"/>
+      <c r="A24" s="125"/>
       <c r="B24" s="11" t="s">
         <v>371</v>
       </c>
@@ -11831,7 +11830,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="126" t="s">
+      <c r="A25" s="125" t="s">
         <v>297</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -11863,7 +11862,7 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="126"/>
+      <c r="A26" s="125"/>
       <c r="B26" s="11" t="s">
         <v>371</v>
       </c>
@@ -11894,17 +11893,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A26"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12173,323 +12172,323 @@
       <c r="A2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="67">
+      <c r="B2" s="126">
         <f>((CES_kor!C8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="C2" s="67">
+      <c r="C2" s="126">
         <f>((CES_kor!D8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="D2" s="67">
+      <c r="D2" s="126">
         <f>((CES_kor!E8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="E2" s="67">
+      <c r="E2" s="126">
         <f>((CES_kor!F8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="F2" s="67">
+      <c r="F2" s="126">
         <f>((CES_kor!G8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="G2" s="67">
+      <c r="G2" s="126">
         <f>((CES_kor!H8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="H2" s="67">
+      <c r="H2" s="126">
         <f>((CES_kor!I8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="I2" s="67">
+      <c r="I2" s="126">
         <f>((CES_kor!J8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="J2" s="67">
+      <c r="J2" s="126">
         <f>((CES_kor!K8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="K2" s="67">
+      <c r="K2" s="126">
         <f>((CES_kor!L8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="L2" s="67">
+      <c r="L2" s="126">
         <f>((CES_kor!M8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="M2" s="67">
+      <c r="M2" s="126">
         <f>((CES_kor!N8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="N2" s="67">
+      <c r="N2" s="126">
         <f>((CES_kor!O8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="O2" s="67">
+      <c r="O2" s="126">
         <f>((CES_kor!P8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="P2" s="67">
+      <c r="P2" s="126">
         <f>((CES_kor!Q8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="Q2" s="67">
+      <c r="Q2" s="126">
         <f>((CES_kor!R8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="R2" s="67">
+      <c r="R2" s="126">
         <f>((CES_kor!S8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="S2" s="67">
+      <c r="S2" s="126">
         <f>((CES_kor!T8)/100)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="T2" s="67">
+      <c r="T2" s="126">
         <f>(S2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="U2" s="67">
+      <c r="U2" s="126">
         <f>(T2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="V2" s="67">
+      <c r="V2" s="126">
         <f>(U2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="W2" s="67">
+      <c r="W2" s="126">
         <f>(V2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="X2" s="67">
+      <c r="X2" s="126">
         <f>(W2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="Y2" s="67">
+      <c r="Y2" s="126">
         <f>(X2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="Z2" s="67">
+      <c r="Z2" s="126">
         <f>(Y2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="AA2" s="67">
+      <c r="AA2" s="126">
         <f>(Z2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="AB2" s="67">
+      <c r="AB2" s="126">
         <f>(AA2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="AC2" s="67">
+      <c r="AC2" s="126">
         <f>(AB2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="AD2" s="67">
+      <c r="AD2" s="126">
         <f>(AC2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="AE2" s="67">
+      <c r="AE2" s="126">
         <f>(AD2)*CES_kor!$B$10</f>
         <v>0</v>
       </c>
-      <c r="AF2" s="67">
+      <c r="AF2" s="126">
         <f t="shared" ref="AF2:AY2" si="0">AE2</f>
         <v>0</v>
       </c>
-      <c r="AG2" s="67">
+      <c r="AG2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH2" s="67">
+      <c r="AH2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AI2" s="67">
+      <c r="AI2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AJ2" s="67">
+      <c r="AJ2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AK2" s="67">
+      <c r="AK2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AL2" s="67">
+      <c r="AL2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM2" s="67">
+      <c r="AM2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN2" s="67">
+      <c r="AN2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AO2" s="67">
+      <c r="AO2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AP2" s="67">
+      <c r="AP2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AQ2" s="67">
+      <c r="AQ2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AR2" s="67">
+      <c r="AR2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AS2" s="67">
+      <c r="AS2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AT2" s="67">
+      <c r="AT2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AU2" s="67">
+      <c r="AU2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AV2" s="67">
+      <c r="AV2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AW2" s="67">
+      <c r="AW2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AX2" s="67">
+      <c r="AX2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AY2" s="67">
+      <c r="AY2" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AZ2" s="67">
+      <c r="AZ2" s="126">
         <f t="shared" ref="AZ2:CC2" si="1">AY2</f>
         <v>0</v>
       </c>
-      <c r="BA2" s="67">
+      <c r="BA2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BB2" s="67">
+      <c r="BB2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BC2" s="67">
+      <c r="BC2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BD2" s="67">
+      <c r="BD2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BE2" s="67">
+      <c r="BE2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BF2" s="67">
+      <c r="BF2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BG2" s="67">
+      <c r="BG2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BH2" s="67">
+      <c r="BH2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BI2" s="67">
+      <c r="BI2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BJ2" s="67">
+      <c r="BJ2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BK2" s="67">
+      <c r="BK2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BL2" s="67">
+      <c r="BL2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BM2" s="67">
+      <c r="BM2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BN2" s="67">
+      <c r="BN2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BO2" s="67">
+      <c r="BO2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BP2" s="67">
+      <c r="BP2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BQ2" s="67">
+      <c r="BQ2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BR2" s="67">
+      <c r="BR2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BS2" s="67">
+      <c r="BS2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BT2" s="67">
+      <c r="BT2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BU2" s="67">
+      <c r="BU2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BV2" s="67">
+      <c r="BV2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BW2" s="67">
+      <c r="BW2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BX2" s="67">
+      <c r="BX2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BY2" s="67">
+      <c r="BY2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BZ2" s="67">
+      <c r="BZ2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CA2" s="67">
+      <c r="CA2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CB2" s="67">
+      <c r="CB2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CC2" s="67">
+      <c r="CC2" s="126">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -41999,18 +41998,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -42158,18 +42157,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E4DC507-1B00-4182-8466-350123371AC7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD26A6D2-559B-4381-A873-3D2325889C28}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD26A6D2-559B-4381-A873-3D2325889C28}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E4DC507-1B00-4182-8466-350123371AC7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
